--- a/AI Audit Log_HoangLan.xlsx
+++ b/AI Audit Log_HoangLan.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -104,6 +104,37 @@
   </si>
   <si>
     <t>Response: AI listed the stages including Planning, Requirement Analysis, Design, Development, Testing, Deployment, and Maintenance, along with outputs such as requirement documents, UML diagrams, source code, testing reports, and maintenance logs.</t>
+  </si>
+  <si>
+    <t>“What are the most common mistakes when drawing a Use Case Diagram in software engineering?”</t>
+  </si>
+  <si>
+    <t>Response: AI explained that common mistakes include connecting actors directly to each other, creating overly detailed use cases, misusing &lt;&lt;include&gt;&gt; and &lt;&lt;extend&gt;&gt; relationships, and drawing unclear system boundaries.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>“Explain the differences between &lt;&lt;include&gt;&gt;, &lt;&lt;extend&gt;&gt;, and generalization relationships in Use Case Diagrams.”</t>
+  </si>
+  <si>
+    <t>Response: AI described &lt;&lt;include&gt;&gt; as mandatory reusable behavior, &lt;&lt;extend&gt;&gt; as optional behavior triggered under certain conditions, and generalization as inheritance between actors or use cases.</t>
+  </si>
+  <si>
+    <t>“How do Use Case Diagrams support communication between developers and stakeholders?”</t>
+  </si>
+  <si>
+    <t>support communication between developers and stakeholders?”
+Response: AI explained that Use Case Diagrams visually represent system functionality, helping developers, clients, and stakeholders understand user interactions without technical implementation details</t>
+  </si>
+  <si>
+    <t>Evaluation + Reflection</t>
+  </si>
+  <si>
+    <t>“How can incorrect Use Case relationships negatively affect system analysis and design?”</t>
+  </si>
+  <si>
+    <t>Response: AI explained that incorrect relationships may create misunderstanding of system behavior, duplicate functionalities, and make diagrams confusing or inconsistent. Misusing &lt;&lt;include&gt;&gt; or &lt;&lt;extend&gt;&gt; can also lead to poor requirement organization</t>
   </si>
 </sst>
 </file>
@@ -136,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -159,11 +190,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -182,6 +224,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20.8984375" customWidth="1"/>
@@ -625,29 +676,61 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="69">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="69">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="82.8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4"/>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="82.8">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
